--- a/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0002T0006Z000C1N93_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0002T0006Z000C1N93_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>53.27317513793629</v>
+        <v>8.656890959914648</v>
       </c>
       <c r="D2" t="n">
-        <v>53.62748060949159</v>
+        <v>8.714465599042384</v>
       </c>
       <c r="E2" t="n">
-        <v>9.853610396953409</v>
+        <v>1.601211689504929</v>
       </c>
       <c r="F2" t="n">
-        <v>9.774155648706472</v>
+        <v>1.588300292914802</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>59.7580974796477</v>
+        <v>9.710690840442751</v>
       </c>
       <c r="D3" t="n">
-        <v>60.11184820273495</v>
+        <v>9.768175332944431</v>
       </c>
       <c r="E3" t="n">
-        <v>9.853610396953409</v>
+        <v>1.601211689504929</v>
       </c>
       <c r="F3" t="n">
-        <v>9.774155648706472</v>
+        <v>1.588300292914802</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>38.57625972950897</v>
+        <v>6.268642206045207</v>
       </c>
       <c r="D4" t="n">
-        <v>38.88301541257909</v>
+        <v>6.318490004544103</v>
       </c>
       <c r="E4" t="n">
-        <v>9.853610396953409</v>
+        <v>1.601211689504929</v>
       </c>
       <c r="F4" t="n">
-        <v>9.774155648706472</v>
+        <v>1.588300292914802</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>39.26397785625993</v>
+        <v>6.380396401642239</v>
       </c>
       <c r="D5" t="n">
-        <v>39.49369061432601</v>
+        <v>6.417724724827977</v>
       </c>
       <c r="E5" t="n">
-        <v>9.853610396953409</v>
+        <v>1.601211689504929</v>
       </c>
       <c r="F5" t="n">
-        <v>9.774155648706472</v>
+        <v>1.588300292914802</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>30.87366978057533</v>
+        <v>5.016971339343491</v>
       </c>
       <c r="D6" t="n">
-        <v>31.25998083214191</v>
+        <v>5.07974688522306</v>
       </c>
       <c r="E6" t="n">
-        <v>9.853610396953409</v>
+        <v>1.601211689504929</v>
       </c>
       <c r="F6" t="n">
-        <v>9.774155648706472</v>
+        <v>1.588300292914802</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>60.49277617138588</v>
+        <v>9.830076127850207</v>
       </c>
       <c r="D7" t="n">
-        <v>60.80065849540522</v>
+        <v>9.880107005503348</v>
       </c>
       <c r="E7" t="n">
-        <v>9.853610396953409</v>
+        <v>1.601211689504929</v>
       </c>
       <c r="F7" t="n">
-        <v>9.774155648706472</v>
+        <v>1.588300292914802</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>56.25727285675443</v>
+        <v>9.141806839222594</v>
       </c>
       <c r="D8" t="n">
-        <v>56.5061076256631</v>
+        <v>9.182242489170253</v>
       </c>
       <c r="E8" t="n">
-        <v>9.853610396953409</v>
+        <v>1.601211689504929</v>
       </c>
       <c r="F8" t="n">
-        <v>9.774155648706472</v>
+        <v>1.588300292914802</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>44.79432266364552</v>
+        <v>7.279077432842397</v>
       </c>
       <c r="D9" t="n">
-        <v>44.65098620829546</v>
+        <v>7.255785258848013</v>
       </c>
       <c r="E9" t="n">
-        <v>9.853610396953409</v>
+        <v>1.601211689504929</v>
       </c>
       <c r="F9" t="n">
-        <v>9.774155648706472</v>
+        <v>1.588300292914802</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>53.62032043414647</v>
+        <v>8.713302070548801</v>
       </c>
       <c r="D10" t="n">
-        <v>53.3320079154399</v>
+        <v>8.666451286258985</v>
       </c>
       <c r="E10" t="n">
-        <v>9.853610396953409</v>
+        <v>1.601211689504929</v>
       </c>
       <c r="F10" t="n">
-        <v>9.774155648706472</v>
+        <v>1.588300292914802</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>64.04797593870637</v>
+        <v>10.40779609003979</v>
       </c>
       <c r="D11" t="n">
-        <v>63.74053406395163</v>
+        <v>10.35783678539214</v>
       </c>
       <c r="E11" t="n">
-        <v>9.853610396953409</v>
+        <v>1.601211689504929</v>
       </c>
       <c r="F11" t="n">
-        <v>9.774155648706472</v>
+        <v>1.588300292914802</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>61.72724812160983</v>
+        <v>10.0306778197616</v>
       </c>
       <c r="D12" t="n">
-        <v>61.36559633055141</v>
+        <v>9.971909403714605</v>
       </c>
       <c r="E12" t="n">
-        <v>9.853610396953409</v>
+        <v>1.601211689504929</v>
       </c>
       <c r="F12" t="n">
-        <v>9.774155648706472</v>
+        <v>1.588300292914802</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>46.44704810046622</v>
+        <v>7.54764531632576</v>
       </c>
       <c r="D13" t="n">
-        <v>46.13693104172911</v>
+        <v>7.497251294280981</v>
       </c>
       <c r="E13" t="n">
-        <v>9.853610396953409</v>
+        <v>1.601211689504929</v>
       </c>
       <c r="F13" t="n">
-        <v>9.774155648706472</v>
+        <v>1.588300292914802</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>46.77077196928335</v>
+        <v>7.600250445008544</v>
       </c>
       <c r="D14" t="n">
-        <v>46.41487635050171</v>
+        <v>7.542417406956528</v>
       </c>
       <c r="E14" t="n">
-        <v>9.853610396953409</v>
+        <v>1.601211689504929</v>
       </c>
       <c r="F14" t="n">
-        <v>9.774155648706472</v>
+        <v>1.588300292914802</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
